--- a/SECRON/recursos/Listado roles y permisos.xlsx
+++ b/SECRON/recursos/Listado roles y permisos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pablo Hernandez\Documents\GitHub\workSpace\SECRONDEV\SECRON\recursos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose_Torres\Documents\GitHub\SECRONDEV\SECRON\recursos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F585EF71-0562-419A-A65A-01A529D5DD48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7152FC3-1AB5-4A8B-A212-15A3DF4CD5C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3FA8ED39-8EDA-441E-B862-25010B086206}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{3FA8ED39-8EDA-441E-B862-25010B086206}"/>
   </bookViews>
   <sheets>
     <sheet name="ROLES" sheetId="1" r:id="rId1"/>
@@ -35401,7 +35401,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="685" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>19</v>
       </c>
@@ -35424,7 +35424,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="686" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>19</v>
       </c>
@@ -35447,7 +35447,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="687" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>19</v>
       </c>
@@ -35470,7 +35470,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="688" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>19</v>
       </c>
@@ -35493,7 +35493,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="689" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>19</v>
       </c>
@@ -35516,7 +35516,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="690" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>19</v>
       </c>
@@ -35539,7 +35539,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="691" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>19</v>
       </c>
@@ -35562,7 +35562,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="692" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>19</v>
       </c>
@@ -35585,7 +35585,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="693" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>19</v>
       </c>
@@ -35608,7 +35608,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="694" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>19</v>
       </c>
@@ -35631,7 +35631,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="695" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>19</v>
       </c>
@@ -35654,7 +35654,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="696" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>19</v>
       </c>
@@ -37379,7 +37379,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="771" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>25</v>
       </c>
@@ -37402,7 +37402,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="772" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>25</v>
       </c>
@@ -37425,7 +37425,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="773" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>25</v>
       </c>
@@ -37448,7 +37448,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="774" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>25</v>
       </c>
@@ -37471,7 +37471,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="775" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>25</v>
       </c>
@@ -37494,7 +37494,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="776" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>25</v>
       </c>
@@ -37517,7 +37517,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="777" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>25</v>
       </c>
@@ -37540,7 +37540,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="778" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>25</v>
       </c>
@@ -37567,7 +37567,7 @@
   <autoFilter ref="A1:G778" xr:uid="{F536E046-9624-4549-BC8D-F58E7E42C701}">
     <filterColumn colId="0">
       <filters>
-        <filter val="ALMACENISTA"/>
+        <filter val="ANALISTA DE RECURSOS HUMANOS"/>
       </filters>
     </filterColumn>
   </autoFilter>
